--- a/outputs/Redditch Library - RFQ Schedule for Supplier.xlsx
+++ b/outputs/Redditch Library - RFQ Schedule for Supplier.xlsx
@@ -473,6 +473,7 @@
       </c>
       <c r="B1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -493,7 +494,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>43 items across 41 references, 136.54 m2 total</t>
+          <t>43 items across 41 references, 136.53 m2 total</t>
         </is>
       </c>
     </row>
